--- a/rules/CORE-000155/negative/01/data/unit-test-coreid-CG0293-negative.xlsx
+++ b/rules/CORE-000155/negative/01/data/unit-test-coreid-CG0293-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulieChason\GitHub\core-contributor\rules\CORE-000155\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D320C8D-58D1-4848-858B-9661A93B7C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F7A82C-5AFB-4528-B02E-D06A604486A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="66">
   <si>
     <t>Product</t>
   </si>
@@ -164,12 +164,6 @@
     <t>SCREENING</t>
   </si>
   <si>
-    <t>PLACEBO</t>
-  </si>
-  <si>
-    <t>TREATMENT</t>
-  </si>
-  <si>
     <t>ZAN_LOW</t>
   </si>
   <si>
@@ -179,12 +173,6 @@
     <t>Randomized to Zanomaline Low Dose</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>Zanomaline 54 mg</t>
-  </si>
-  <si>
     <t>ZAN_HIGH</t>
   </si>
   <si>
@@ -192,18 +180,6 @@
   </si>
   <si>
     <t>Randomized to Zanomaline High Dose</t>
-  </si>
-  <si>
-    <t>TITRATE</t>
-  </si>
-  <si>
-    <t>Zanomaline 54 mg Titration</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>Zanomaline 81 mg</t>
   </si>
   <si>
     <t>VISITNUM</t>
@@ -729,7 +705,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6">
         <v>5</v>
@@ -738,7 +714,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -748,7 +724,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
@@ -908,7 +884,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>38</v>
       </c>
@@ -916,22 +892,25 @@
         <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="72.900000000000006" x14ac:dyDescent="0.4">
@@ -942,10 +921,10 @@
         <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
@@ -957,143 +936,10 @@
         <v>43</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="4">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="4">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="4">
-        <v>3</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="4">
-        <v>4</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1114,19 +960,19 @@
         <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
@@ -1137,19 +983,19 @@
         <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -1203,22 +1049,22 @@
         <v>38</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
